--- a/etudecas/donnees/021081.xlsx
+++ b/etudecas/donnees/021081.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://scalian-my.sharepoint.com/personal/yannick_martz_scalian_com/Documents/0_FILES_YM/2026/Pierre Fabre/Data/safe/IN/PF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\lca-simu\etudecas\donnees\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{F1B106E4-76CD-4A29-A43F-305A6627139B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{895D7200-E97F-47B3-8318-E155AEE945B7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982F8105-01B0-4857-BD7D-FE66A033610E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -613,7 +613,7 @@
     <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.77734375" customWidth="1"/>
+    <col min="7" max="7" width="46.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -688,7 +688,7 @@
         <v>120</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>20000</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
@@ -714,7 +714,7 @@
         <v>120</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>20000</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
@@ -775,6 +775,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002D5C0BAE13F791428A2467AD4E2CA4A9" ma:contentTypeVersion="3" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="e041f94258a4985e0980ebef8737f2c5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="911fa86e-1244-486f-9d05-850c48c46759" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="44562186199d162c4fe6c5d19537b3b1" ns2:_="">
     <xsd:import namespace="911fa86e-1244-486f-9d05-850c48c46759"/>
@@ -912,12 +918,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16A7D708-177D-45A8-9A9F-54519F149F23}">
   <ds:schemaRefs>
@@ -927,6 +927,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0FB338B-ED0A-4F1D-9C17-408B90846938}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="911fa86e-1244-486f-9d05-850c48c46759"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB4FDE94-F1D1-4D92-9E5B-BE9D0325F69C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -942,20 +958,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0FB338B-ED0A-4F1D-9C17-408B90846938}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="911fa86e-1244-486f-9d05-850c48c46759"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>